--- a/Luban/Config/Datas/Levels/L05/EnemyList.xlsx
+++ b/Luban/Config/Datas/Levels/L05/EnemyList.xlsx
@@ -1158,7 +1158,7 @@
       </c>
       <c r="C4" s="0" t="inlineStr">
         <is>
-          <t>10016976,10016982,10016978,10048510,10016981,10016979,10016976,10016982,10016978,10048510,10016981,10016979,10016976,10016982,10016978,10048510,10016981,10016979,10016976,10016982,10016978,10048510,10016981,10016979,10016976,10016982,10016978,10016973,10016981,10016980,10016976,10016982,10016978,10016973,10016981,10016980,10016976,10016982,10016978,10016973,10016981,10016980,10016976,10016982,10016978,10016973,10016981,10016983,10016976,10016982,10016978,10048511,10016986,10016983,10016976,10016982,10016985,10048511,10016986,10016983,10016976,10016982,10016985,10048511,10016986,10016983,10016976,10016982,10016985,10048511,10016986,10016984,10016976,10016982,10016985,10016974,10016986,10016984,10016976,10016982,10016985,10016974,10016986,10016984,10016976,10016982,10016985,10016974,10016986,10016984,10016976,10016982,10016985,10016975,10016986,10016976,10016982,10016985,10016975,10016987,10016976,10016982,10016985,10016975,10016987,10016977,10016982,10016975,10016987,10016977,10016982,10016987,10016977,10016982,10016987,10016977,10016982,10016987,10016977,10016982,10016987,10016977,10016982,10016977,10016982,10016977,10016982,10016977,10016982,10016977,10016982,10016977,10016982,10016977,10016982,10016977,10016982,10016977,10016982,10016977,10016982,10016977,10016982,10016977,10016982,10016977,10016982,10016977,10016982,10016982,10016982,10016982,10016982,10016982,10016982</t>
+          <t>10016976,10048510,10016978,10048510,10016981,10016979,10016976,10048510,10016978,10048510,10016981,10016979,10016976,10048510,10016978,10048510,10016981,10016979,10016976,10048510,10016978,10048510,10016981,10016979,10016976,10016973,10016978,10016973,10016981,10016980,10016976,10016973,10016978,10016973,10016981,10016980,10016976,10016973,10016978,10016973,10016981,10016980,10016976,10016973,10016978,10016973,10016981,10016983,10016976,10048511,10016978,10048511,10016986,10016983,10016976,10048511,10016985,10048511,10016986,10016983,10016976,10048511,10016985,10048511,10016986,10016983,10016976,10048511,10016985,10048511,10016986,10016984,10016976,10016974,10016985,10016974,10016986,10016984,10016976,10016974,10016985,10016974,10016986,10016984,10016976,10016974,10016985,10016974,10016986,10016984,10016976,10016975,10016985,10016975,10016986,10016976,10016975,10016985,10016975,10016987,10016976,10016975,10016985,10016975,10016987,10016977,10016975,10016975,10016987,10016977,10016982,10016987,10016977,10016982,10016987,10016977,10016982,10016987,10016977,10016982,10016987,10016977,10016982,10016977,10016982,10016977,10016982,10016977,10016982,10016977,10016982,10016977,10016982,10016977,10016982,10016977,10016982,10016977,10016982,10016977,10016982,10016977,10016982,10016977,10016982,10016977,10016982,10016977,10016982,10016982,10016982,10016982,10016982,10016982,10016982</t>
         </is>
       </c>
       <c r="D4" s="3" t="n">
@@ -1169,7 +1169,7 @@
       </c>
       <c r="F4" s="0" t="inlineStr">
         <is>
-          <t>L5 W21/25; N=155; EHP=16551.000000; air:2x4,air:11x4,air:12x4,air:13x3,air:14x4,normal:17x18,normal:18x19,fast:30x9,heavy:31x4,heavy:80x3,medium:83x8,swarm:84x43,heavy:86x4,heavy:88x4,fast:98x9,medium:108x8,medium:123x7</t>
+          <t>L5 W21/25; N=155; EHP=30605.087972; air:2x8,air:11x8,air:12x8,air:13x6,air:14x8,fast:30x9,fast:98x9,heavy:31x4,heavy:80x3,heavy:86x4,heavy:88x4,medium:83x8,medium:108x8,medium:123x7,normal:17x18,normal:18x19,swarm:84x24 | manual: L1-scaled</t>
         </is>
       </c>
     </row>
@@ -1179,7 +1179,7 @@
       </c>
       <c r="C5" s="0" t="inlineStr">
         <is>
-          <t>10016991,10016997,10016993,10048512,10016996,10016994,10016991,10016997,10016993,10048512,10016996,10016994,10016991,10016997,10016993,10048512,10016996,10016994,10016991,10016997,10016993,10048512,10016996,10016994,10016991,10016997,10016993,10016988,10016996,10016995,10016991,10016997,10016993,10016988,10016996,10016995,10016991,10016997,10016993,10016988,10016996,10016995,10016991,10016997,10016993,10048513,10016996,10016995,10016991,10016997,10016993,10048513,10017001,10016998,10016991,10016997,10017000,10048513,10017001,10016998,10016991,10016997,10017000,10048513,10017001,10016998,10016991,10016997,10017000,10016989,10017001,10016998,10016991,10016997,10017000,10016989,10017001,10016999,10016991,10016997,10017000,10016989,10017001,10016999,10016991,10016997,10017000,10016989,10017001,10016999,10016991,10016997,10017000,10016990,10017001,10016999,10016991,10016997,10017000,10016990,10017002,10016991,10016997,10017000,10016990,10017002,10016991,10016997,10017000,10016990,10017002,10016992,10016997,10017002,10016992,10016997,10017002,10016992,10016997,10017002,10016992,10016997,10017002,10016992,10016997,10017002,10016992,10016997,10016992,10016997,10016992,10016997,10016992,10016997,10016992,10016997,10016992,10016997,10016992,10016997,10016992,10016997,10016992,10016997,10016992,10016997,10016992,10016997,10016992,10016997,10016992,10016997,10016992,10016997,10016997,10016997,10016997,10016997,10016997,10016997,10016997</t>
+          <t>10016991,10048512,10016993,10048512,10016996,10016994,10016991,10048512,10016993,10048512,10016996,10016994,10016991,10048512,10016993,10048512,10016996,10016994,10016991,10048512,10016993,10048512,10016996,10016994,10016991,10016988,10016993,10016988,10016996,10016995,10016991,10016988,10016993,10016988,10016996,10016995,10016991,10016988,10016993,10016988,10016996,10016995,10016991,10048513,10016993,10048513,10016996,10016995,10016991,10048513,10016993,10048513,10017001,10016998,10016991,10048513,10017000,10048513,10017001,10016998,10016991,10048513,10017000,10048513,10017001,10016998,10016991,10016989,10017000,10016989,10017001,10016998,10016991,10016989,10017000,10016989,10017001,10016999,10016991,10016989,10017000,10016989,10017001,10016999,10016991,10016989,10017000,10016989,10017001,10016999,10016991,10016990,10017000,10016990,10017001,10016999,10016991,10016990,10017000,10016990,10017002,10016991,10016990,10017000,10016990,10017002,10016991,10016990,10017000,10016990,10017002,10016992,10016997,10017002,10016992,10016997,10017002,10016992,10016997,10017002,10016992,10016997,10017002,10016992,10016997,10017002,10016992,10016997,10016992,10016997,10016992,10016997,10016992,10016997,10016992,10016997,10016992,10016997,10016992,10016997,10016992,10016997,10016992,10016997,10016992,10016997,10016992,10016997,10016992,10016997,10016992,10016997,10016992,10016997,10016997,10016997,10016997,10016997,10016997,10016997,10016997</t>
         </is>
       </c>
       <c r="D5" s="3" t="n">
@@ -1190,7 +1190,7 @@
       </c>
       <c r="F5" s="0" t="inlineStr">
         <is>
-          <t>L5 W22/25; N=161; EHP=16883.000000; air:2x4,air:11x3,air:12x4,air:13x4,air:14x4,normal:17x19,normal:18x19,fast:30x9,heavy:31x4,heavy:80x4,medium:83x8,swarm:84x45,heavy:86x4,heavy:88x4,fast:98x10,medium:108x8,medium:123x8</t>
+          <t>L5 W22/25; N=161; EHP=31203.707667; air:2x8,air:11x6,air:12x8,air:13x8,air:14x8,fast:30x9,fast:98x10,heavy:31x4,heavy:80x4,heavy:86x4,heavy:88x4,medium:83x8,medium:108x8,medium:123x8,normal:17x19,normal:18x19,swarm:84x26 | manual: L1-scaled</t>
         </is>
       </c>
     </row>
@@ -1211,7 +1211,7 @@
       </c>
       <c r="F6" s="0" t="inlineStr">
         <is>
-          <t>L5 W1/25; N=35; EHP=198.660000; normal:17x17,normal:18x18</t>
+          <t>L5 W1/25; N=35; EHP=363.062562; normal:17x17,normal:18x18 | manual: L1-scaled</t>
         </is>
       </c>
     </row>
@@ -1232,7 +1232,7 @@
       </c>
       <c r="F7" s="0" t="inlineStr">
         <is>
-          <t>L5 W2/25; N=41; EHP=243.676924; normal:17x21,normal:18x20</t>
+          <t>L5 W2/25; N=41; EHP=445.333576; normal:17x21,normal:18x20 | manual: L1-scaled</t>
         </is>
       </c>
     </row>
@@ -1242,7 +1242,7 @@
       </c>
       <c r="C8" s="0" t="inlineStr">
         <is>
-          <t>3264136,3264673,3264019,3264136,3264673,3264091,3264136,3264673,3264099,3264136,3264673,3264099,3264136,3264673,3264107,3264136,3264673,3264115,3264136,3264673,3264136,3264673,3264136,3264673,3264136,3264673,3264136,3264673,3264136,3264673,3264136,3264673,3264136,3264144,3264144,3264144,3264144,3264144,3264144,3264144,3264144,3264144,3264144,3264144,3264144,3264144,3264144</t>
+          <t>3264136,3264673,3264136,3264673,3264136,3264673,3264136,3264673,3264136,3264673,3264136,3264673,3264136,3264673,3264136,3264673,3264136,3264673,3264136,3264673,3264136,3264673,3264136,3264673,3264136,3264673,3264136,3264144,3264144,3264144,3264144,3264144,3264144,3264144,3264144,3264144,3264144,3264144,3264144,3264144,3264144,3264136,3264136,3264136,3264136,3264136,3264136</t>
         </is>
       </c>
       <c r="D8" s="0" t="n">
@@ -1253,7 +1253,7 @@
       </c>
       <c r="F8" s="0" t="inlineStr">
         <is>
-          <t>L5 W3/25; N=47; EHP=309.028685; air:2x1,air:11x1,air:12x2,air:13x1,air:14x1,normal:17x14,normal:18x14,swarm:84x13</t>
+          <t>L5 W3/25; N=47; EHP=612.372612; normal:17x20,normal:18x14,swarm:84x13 | manual: L1-scaled</t>
         </is>
       </c>
     </row>
@@ -1263,7 +1263,7 @@
       </c>
       <c r="C9" s="0" t="inlineStr">
         <is>
-          <t>3266136,3266673,3266019,3266136,3266673,3266019,3266136,3266673,3266091,3266136,3266673,3266099,3266136,3266673,3266107,3266136,3266673,3266115,3266136,3266673,3266136,3266673,3266136,3266673,3266136,3266673,3266136,3266673,3266136,3266673,3266136,3266673,3266136,3266673,3266136,3266136,3266136,3266144,3266144,3266144,3266144,3266144,3266144,3266144,3266144,3266144,3266144,3266144,3266144,3266144,3266144,3266144,3266144</t>
+          <t>3266136,3266673,3266136,3266673,3266136,3266673,3266136,3266673,3266136,3266673,3266136,3266673,3266136,3266673,3266136,3266673,3266136,3266673,3266136,3266673,3266136,3266673,3266136,3266673,3266136,3266673,3266136,3266673,3266136,3266136,3266136,3266144,3266144,3266144,3266144,3266144,3266144,3266144,3266144,3266144,3266144,3266144,3266144,3266144,3266144,3266144,3266144,3266136,3266136,3266136,3266136,3266136,3266136</t>
         </is>
       </c>
       <c r="D9" s="0" t="n">
@@ -1274,7 +1274,7 @@
       </c>
       <c r="F9" s="0" t="inlineStr">
         <is>
-          <t>L5 W4/25; N=53; EHP=401.274469; air:2x2,air:11x1,air:12x1,air:13x1,air:14x1,normal:17x17,normal:18x16,swarm:84x14</t>
+          <t>L5 W4/25; N=53; EHP=787.371387; normal:17x23,normal:18x16,swarm:84x14 | manual: L1-scaled</t>
         </is>
       </c>
     </row>
@@ -1284,7 +1284,7 @@
       </c>
       <c r="C10" s="0" t="inlineStr">
         <is>
-          <t>3268136,3268673,3268019,3268668,3268136,3268673,3268091,3268668,3268136,3268673,3268091,3268868,3268136,3268673,3268099,3268868,3268136,3268673,3268107,3268868,3268136,3268673,3268107,3268988,3268136,3268673,3268115,3268988,3268136,3268673,3268988,3268136,3268673,3268136,3268673,3268136,3268673,3268136,3268673,3268136,3268673,3268136,3268673,3268144,3268673,3268144,3268673,3268144,3268144,3268144,3268144,3268144,3268144,3268144,3268144,3268144,3268144,3268144,3268144</t>
+          <t>3268136,3268019,3268019,3268668,3268136,3268091,3268091,3268668,3268136,3268091,3268091,3268868,3268136,3268099,3268099,3268868,3268136,3268107,3268107,3268868,3268136,3268107,3268107,3268988,3268136,3268115,3268115,3268988,3268136,3268673,3268988,3268136,3268673,3268136,3268673,3268136,3268673,3268136,3268673,3268136,3268673,3268136,3268673,3268144,3268673,3268144,3268673,3268144,3268144,3268144,3268144,3268144,3268144,3268144,3268144,3268144,3268144,3268144,3268144</t>
         </is>
       </c>
       <c r="D10" s="0" t="n">
@@ -1295,7 +1295,7 @@
       </c>
       <c r="F10" s="0" t="inlineStr">
         <is>
-          <t>L5 W5/25; N=59; EHP=769.381255; air:2x1,air:11x2,air:12x1,air:13x2,air:14x1,normal:17x14,normal:18x14,medium:83x2,swarm:84x16,medium:108x3,medium:123x3</t>
+          <t>L5 W5/25; N=59; EHP=1423.935439; air:2x2,air:11x4,air:12x2,air:13x4,air:14x2,medium:83x2,medium:108x3,medium:123x3,normal:17x14,normal:18x14,swarm:84x9 | manual: L1-scaled</t>
         </is>
       </c>
     </row>
@@ -1305,7 +1305,7 @@
       </c>
       <c r="C11" s="0" t="inlineStr">
         <is>
-          <t>3270136,3270673,3270242,3270019,3270668,3270136,3270673,3270242,3270091,3270668,3270136,3270673,3270242,3270091,3270668,3270136,3270673,3270786,3270099,3270868,3270136,3270673,3270786,3270099,3270868,3270136,3270673,3270786,3270107,3270868,3270136,3270673,3270786,3270115,3270988,3270136,3270673,3270115,3270988,3270136,3270673,3270988,3270136,3270673,3270136,3270673,3270136,3270673,3270144,3270673,3270144,3270673,3270144,3270673,3270144,3270673,3270144,3270673,3270144,3270673,3270144,3270144,3270144,3270144,3270144</t>
+          <t>3270136,3270019,3270242,3270019,3270668,3270136,3270091,3270242,3270091,3270668,3270136,3270091,3270242,3270091,3270668,3270136,3270099,3270786,3270099,3270868,3270136,3270099,3270786,3270099,3270868,3270136,3270107,3270786,3270107,3270868,3270136,3270115,3270786,3270115,3270988,3270136,3270115,3270115,3270988,3270136,3270673,3270988,3270136,3270673,3270136,3270673,3270136,3270673,3270144,3270673,3270144,3270673,3270144,3270673,3270144,3270673,3270144,3270673,3270144,3270673,3270144,3270144,3270144,3270144,3270144</t>
         </is>
       </c>
       <c r="D11" s="0" t="n">
@@ -1316,7 +1316,7 @@
       </c>
       <c r="F11" s="0" t="inlineStr">
         <is>
-          <t>L5 W6/25; N=65; EHP=785.000000; air:2x1,air:11x2,air:12x2,air:13x1,air:14x2,normal:17x12,normal:18x11,fast:30x3,medium:83x3,swarm:84x18,fast:98x4,medium:108x3,medium:123x3</t>
+          <t>L5 W6/25; N=65; EHP=1453.905577; air:2x2,air:11x4,air:12x4,air:13x2,air:14x4,fast:30x3,fast:98x4,medium:83x3,medium:108x3,medium:123x3,normal:17x12,normal:18x11,swarm:84x10 | manual: L1-scaled</t>
         </is>
       </c>
     </row>
@@ -1326,7 +1326,7 @@
       </c>
       <c r="C12" s="0" t="inlineStr">
         <is>
-          <t>3272136,3272673,3272242,3272019,3272668,3272136,3272673,3272242,3272019,3272668,3272136,3272673,3272242,3272091,3272668,3272136,3272673,3272242,3272099,3272668,3272136,3272673,3272786,3272099,3272868,3272136,3272673,3272786,3272107,3272868,3272136,3272673,3272786,3272107,3272868,3272136,3272673,3272786,3272115,3272988,3272136,3272673,3272115,3272988,3272136,3272673,3272988,3272136,3272673,3272136,3272673,3272144,3272673,3272144,3272673,3272144,3272673,3272144,3272673,3272144,3272673,3272144,3272673,3272144,3272673,3272144,3272144,3272144,3272144,3272144,3272144</t>
+          <t>3272136,3272019,3272242,3272019,3272668,3272136,3272019,3272242,3272019,3272668,3272136,3272091,3272242,3272091,3272668,3272136,3272099,3272242,3272099,3272668,3272136,3272099,3272786,3272099,3272868,3272136,3272107,3272786,3272107,3272868,3272136,3272107,3272786,3272107,3272868,3272136,3272115,3272786,3272115,3272988,3272136,3272115,3272115,3272988,3272136,3272673,3272988,3272136,3272673,3272136,3272673,3272144,3272673,3272144,3272673,3272144,3272673,3272144,3272673,3272144,3272673,3272144,3272673,3272144,3272673,3272144,3272144,3272144,3272144,3272144,3272144</t>
         </is>
       </c>
       <c r="D12" s="0" t="n">
@@ -1337,7 +1337,7 @@
       </c>
       <c r="F12" s="0" t="inlineStr">
         <is>
-          <t>L5 W7/25; N=71; EHP=904.967818; air:2x2,air:11x1,air:12x2,air:13x2,air:14x2,normal:17x12,normal:18x13,fast:30x4,medium:83x4,swarm:84x19,fast:98x4,medium:108x3,medium:123x3</t>
+          <t>L5 W7/25; N=71; EHP=1676.710314; air:2x4,air:11x2,air:12x4,air:13x4,air:14x4,fast:30x4,fast:98x4,medium:83x4,medium:108x3,medium:123x3,normal:17x12,normal:18x13,swarm:84x10 | manual: L1-scaled</t>
         </is>
       </c>
     </row>
@@ -1347,7 +1347,7 @@
       </c>
       <c r="C13" s="0" t="inlineStr">
         <is>
-          <t>3274136,3274673,3274242,3274019,3274668,3274136,3274673,3274242,3274019,3274668,3274136,3274673,3274242,3274091,3274668,3274136,3274673,3274242,3274091,3274868,3274136,3274673,3274786,3274099,3274868,3274136,3274673,3274786,3274099,3274868,3274136,3274673,3274786,3274107,3274868,3274136,3274673,3274786,3274107,3274988,3274136,3274673,3274786,3274115,3274988,3274136,3274673,3274988,3274136,3274673,3274988,3274136,3274673,3274136,3274673,3274136,3274673,3274144,3274673,3274144,3274673,3274144,3274673,3274144,3274673,3274144,3274673,3274144,3274673,3274144,3274673,3274144,3274144,3274144,3274144,3274144,3274144</t>
+          <t>3274136,3274019,3274242,3274019,3274668,3274136,3274019,3274242,3274019,3274668,3274136,3274091,3274242,3274091,3274668,3274136,3274091,3274242,3274091,3274868,3274136,3274099,3274786,3274099,3274868,3274136,3274099,3274786,3274099,3274868,3274136,3274107,3274786,3274107,3274868,3274136,3274107,3274786,3274107,3274988,3274136,3274115,3274786,3274115,3274988,3274136,3274673,3274988,3274136,3274673,3274988,3274136,3274673,3274136,3274673,3274136,3274673,3274144,3274673,3274144,3274673,3274144,3274673,3274144,3274673,3274144,3274673,3274144,3274673,3274144,3274673,3274144,3274144,3274144,3274144,3274144,3274144</t>
         </is>
       </c>
       <c r="D13" s="0" t="n">
@@ -1358,7 +1358,7 @@
       </c>
       <c r="F13" s="0" t="inlineStr">
         <is>
-          <t>L5 W8/25; N=77; EHP=1170.381551; air:2x2,air:11x2,air:12x2,air:13x2,air:14x1,normal:17x14,normal:18x13,fast:30x4,medium:83x3,swarm:84x21,fast:98x5,medium:108x4,medium:123x4</t>
+          <t>L5 W8/25; N=77; EHP=2166.033755; air:2x4,air:11x4,air:12x4,air:13x4,air:14x2,fast:30x4,fast:98x5,medium:83x3,medium:108x4,medium:123x4,normal:17x14,normal:18x13,swarm:84x12 | manual: L1-scaled</t>
         </is>
       </c>
     </row>
@@ -1368,7 +1368,7 @@
       </c>
       <c r="C14" s="0" t="inlineStr">
         <is>
-          <t>3276136,3276673,3276242,3276019,3276668,3276136,3276673,3276242,3276019,3276668,3276136,3276673,3276242,3276091,3276668,3276136,3276673,3276242,3276091,3276668,3276136,3276673,3276242,3276099,3276868,3276136,3276673,3276786,3276099,3276868,3276136,3276673,3276786,3276107,3276868,3276136,3276673,3276786,3276107,3276868,3276136,3276673,3276786,3276115,3276988,3276136,3276673,3276115,3276988,3276136,3276673,3276988,3276136,3276673,3276988,3276136,3276673,3276136,3276673,3276144,3276673,3276144,3276673,3276144,3276673,3276144,3276673,3276144,3276673,3276144,3276673,3276144,3276673,3276144,3276673,3276144,3276673,3276144,3276144,3276144,3276144,3276144,3276144</t>
+          <t>3276136,3276019,3276242,3276019,3276668,3276136,3276019,3276242,3276019,3276668,3276136,3276091,3276242,3276091,3276668,3276136,3276091,3276242,3276091,3276668,3276136,3276099,3276242,3276099,3276868,3276136,3276099,3276786,3276099,3276868,3276136,3276107,3276786,3276107,3276868,3276136,3276107,3276786,3276107,3276868,3276136,3276115,3276786,3276115,3276988,3276136,3276115,3276115,3276988,3276136,3276673,3276988,3276136,3276673,3276988,3276136,3276673,3276136,3276673,3276144,3276673,3276144,3276673,3276144,3276673,3276144,3276673,3276144,3276673,3276144,3276673,3276144,3276673,3276144,3276673,3276144,3276673,3276144,3276144,3276144,3276144,3276144,3276144</t>
         </is>
       </c>
       <c r="D14" s="0" t="n">
@@ -1379,7 +1379,7 @@
       </c>
       <c r="F14" s="0" t="inlineStr">
         <is>
-          <t>L5 W9/25; N=83; EHP=1496.000000; air:2x2,air:11x2,air:12x2,air:13x2,air:14x2,normal:17x14,normal:18x15,fast:30x5,medium:83x4,swarm:84x23,fast:98x4,medium:108x4,medium:123x4</t>
+          <t>L5 W9/25; N=83; EHP=2769.764840; air:2x4,air:11x4,air:12x4,air:13x4,air:14x4,fast:30x5,fast:98x4,medium:83x4,medium:108x4,medium:123x4,normal:17x14,normal:18x15,swarm:84x13 | manual: L1-scaled</t>
         </is>
       </c>
     </row>
@@ -1389,7 +1389,7 @@
       </c>
       <c r="C15" s="0" t="inlineStr">
         <is>
-          <t>3278136,3278673,3278242,3278019,3278668,3278136,3278673,3278242,3278019,3278668,3278136,3278673,3278242,3278091,3278668,3278136,3278673,3278242,3278091,3278668,3278136,3278673,3278242,3278099,3278668,3278136,3278673,3278786,3278099,3278868,3278136,3278673,3278786,3278107,3278868,3278136,3278673,3278786,3278107,3278868,3278136,3278673,3278786,3278107,3278868,3278136,3278673,3278786,3278115,3278988,3278136,3278673,3278115,3278988,3278136,3278673,3278988,3278136,3278673,3278988,3278136,3278673,3278136,3278673,3278136,3278673,3278144,3278673,3278144,3278673,3278144,3278673,3278144,3278673,3278144,3278673,3278144,3278673,3278144,3278673,3278144,3278673,3278144,3278144,3278144,3278144,3278144,3278144,3278144</t>
+          <t>3278136,3278019,3278242,3278019,3278668,3278136,3278019,3278242,3278019,3278668,3278136,3278091,3278242,3278091,3278668,3278136,3278091,3278242,3278091,3278668,3278136,3278099,3278242,3278099,3278668,3278136,3278099,3278786,3278099,3278868,3278136,3278107,3278786,3278107,3278868,3278136,3278107,3278786,3278107,3278868,3278136,3278107,3278786,3278107,3278868,3278136,3278115,3278786,3278115,3278988,3278136,3278115,3278115,3278988,3278136,3278673,3278988,3278136,3278673,3278988,3278136,3278673,3278136,3278673,3278136,3278673,3278144,3278673,3278144,3278673,3278144,3278673,3278144,3278673,3278144,3278673,3278144,3278673,3278144,3278673,3278144,3278673,3278144,3278144,3278144,3278144,3278144,3278144,3278144</t>
         </is>
       </c>
       <c r="D15" s="0" t="n">
@@ -1400,7 +1400,7 @@
       </c>
       <c r="F15" s="0" t="inlineStr">
         <is>
-          <t>L5 W10/25; N=89; EHP=2763.000000; air:2x2,air:11x2,air:12x2,air:13x3,air:14x2,normal:17x16,normal:18x15,fast:30x5,medium:83x5,swarm:84x24,fast:98x5,medium:108x4,medium:123x4</t>
+          <t>L5 W10/25; N=89; EHP=5117.155286; air:2x4,air:11x4,air:12x4,air:13x6,air:14x4,fast:30x5,fast:98x5,medium:83x5,medium:108x4,medium:123x4,normal:17x16,normal:18x15,swarm:84x13 | manual: L1-scaled</t>
         </is>
       </c>
     </row>
@@ -1410,7 +1410,7 @@
       </c>
       <c r="C16" s="0" t="inlineStr">
         <is>
-          <t>3280136,3280673,3280242,3280019,3280668,3280253,3280136,3280673,3280242,3280019,3280668,3280253,3280136,3280673,3280242,3280091,3280668,3280645,3280136,3280673,3280242,3280091,3280668,3280645,3280136,3280673,3280242,3280091,3280868,3280693,3280136,3280673,3280242,3280099,3280868,3280693,3280136,3280673,3280786,3280099,3280868,3280709,3280136,3280673,3280786,3280107,3280868,3280709,3280136,3280673,3280786,3280107,3280868,3280709,3280136,3280673,3280786,3280115,3280988,3280136,3280673,3280786,3280115,3280988,3280136,3280673,3280988,3280144,3280673,3280988,3280144,3280673,3280988,3280144,3280673,3280144,3280673,3280144,3280673,3280144,3280673,3280144,3280673,3280144,3280673,3280144,3280673,3280144,3280673,3280144,3280673,3280144,3280673,3280673,3280673</t>
+          <t>3280136,3280019,3280242,3280019,3280668,3280253,3280136,3280019,3280242,3280019,3280668,3280253,3280136,3280091,3280242,3280091,3280668,3280645,3280136,3280091,3280242,3280091,3280668,3280645,3280136,3280091,3280242,3280091,3280868,3280693,3280136,3280099,3280242,3280099,3280868,3280693,3280136,3280099,3280786,3280099,3280868,3280709,3280136,3280107,3280786,3280107,3280868,3280709,3280136,3280107,3280786,3280107,3280868,3280709,3280136,3280115,3280786,3280115,3280988,3280136,3280115,3280786,3280115,3280988,3280136,3280673,3280988,3280144,3280673,3280988,3280144,3280673,3280988,3280144,3280673,3280144,3280673,3280144,3280673,3280144,3280673,3280144,3280673,3280144,3280673,3280144,3280673,3280144,3280673,3280144,3280673,3280144,3280673,3280673,3280673</t>
         </is>
       </c>
       <c r="D16" s="0" t="n">
@@ -1421,7 +1421,7 @@
       </c>
       <c r="F16" s="0" t="inlineStr">
         <is>
-          <t>L5 W11/25; N=95; EHP=2819.000000; air:2x2,air:11x3,air:12x2,air:13x2,air:14x2,normal:17x12,normal:18x12,fast:30x6,heavy:31x2,heavy:80x2,medium:83x4,swarm:84x26,heavy:86x2,heavy:88x3,fast:98x5,medium:108x5,medium:123x5</t>
+          <t>L5 W11/25; N=95; EHP=5209.243477; air:2x4,air:11x6,air:12x4,air:13x4,air:14x4,fast:30x6,fast:98x5,heavy:31x2,heavy:80x2,heavy:86x2,heavy:88x3,medium:83x4,medium:108x5,medium:123x5,normal:17x12,normal:18x12,swarm:84x15 | manual: L1-scaled</t>
         </is>
       </c>
     </row>
@@ -1431,7 +1431,7 @@
       </c>
       <c r="C17" s="0" t="inlineStr">
         <is>
-          <t>3282136,3282673,3282242,3282019,3282668,3282253,3282136,3282673,3282242,3282019,3282668,3282253,3282136,3282673,3282242,3282091,3282668,3282645,3282136,3282673,3282242,3282091,3282668,3282645,3282136,3282673,3282242,3282099,3282668,3282645,3282136,3282673,3282242,3282099,3282868,3282693,3282136,3282673,3282786,3282099,3282868,3282693,3282136,3282673,3282786,3282107,3282868,3282693,3282136,3282673,3282786,3282107,3282868,3282709,3282136,3282673,3282786,3282115,3282868,3282709,3282136,3282673,3282786,3282115,3282988,3282136,3282673,3282786,3282115,3282988,3282144,3282673,3282988,3282144,3282673,3282988,3282144,3282673,3282988,3282144,3282673,3282144,3282673,3282144,3282673,3282144,3282673,3282144,3282673,3282144,3282673,3282144,3282673,3282144,3282673,3282144,3282673,3282673,3282673,3282673,3282673</t>
+          <t>3282136,3282019,3282242,3282019,3282668,3282253,3282136,3282019,3282242,3282019,3282668,3282253,3282136,3282091,3282242,3282091,3282668,3282645,3282136,3282091,3282242,3282091,3282668,3282645,3282136,3282099,3282242,3282099,3282668,3282645,3282136,3282099,3282242,3282099,3282868,3282693,3282136,3282099,3282786,3282099,3282868,3282693,3282136,3282107,3282786,3282107,3282868,3282693,3282136,3282107,3282786,3282107,3282868,3282709,3282136,3282115,3282786,3282115,3282868,3282709,3282136,3282115,3282786,3282115,3282988,3282136,3282115,3282786,3282115,3282988,3282144,3282673,3282988,3282144,3282673,3282988,3282144,3282673,3282988,3282144,3282673,3282144,3282673,3282144,3282673,3282144,3282673,3282144,3282673,3282144,3282673,3282144,3282673,3282144,3282673,3282144,3282673,3282673,3282673,3282673,3282673</t>
         </is>
       </c>
       <c r="D17" s="0" t="n">
@@ -1442,7 +1442,7 @@
       </c>
       <c r="F17" s="0" t="inlineStr">
         <is>
-          <t>L5 W12/25; N=101; EHP=2918.000000; air:2x2,air:11x2,air:12x3,air:13x2,air:14x3,normal:17x12,normal:18x12,fast:30x6,heavy:31x2,heavy:80x3,medium:83x5,swarm:84x28,heavy:86x3,heavy:88x2,fast:98x6,medium:108x5,medium:123x5</t>
+          <t>L5 W12/25; N=101; EHP=5393.585420; air:2x4,air:11x4,air:12x6,air:13x4,air:14x6,fast:30x6,fast:98x6,heavy:31x2,heavy:80x3,heavy:86x3,heavy:88x2,medium:83x5,medium:108x5,medium:123x5,normal:17x12,normal:18x12,swarm:84x16 | manual: L1-scaled</t>
         </is>
       </c>
     </row>
@@ -1452,7 +1452,7 @@
       </c>
       <c r="C18" s="0" t="inlineStr">
         <is>
-          <t>3284136,3284673,3284242,3284019,3284668,3284253,3284136,3284673,3284242,3284019,3284668,3284253,3284136,3284673,3284242,3284019,3284668,3284253,3284136,3284673,3284242,3284091,3284668,3284645,3284136,3284673,3284242,3284091,3284668,3284645,3284136,3284673,3284242,3284099,3284668,3284693,3284136,3284673,3284786,3284099,3284868,3284693,3284136,3284673,3284786,3284099,3284868,3284693,3284136,3284673,3284786,3284107,3284868,3284709,3284136,3284673,3284786,3284107,3284868,3284709,3284136,3284673,3284786,3284107,3284868,3284136,3284673,3284786,3284115,3284988,3284136,3284673,3284115,3284988,3284144,3284673,3284988,3284144,3284673,3284988,3284144,3284673,3284988,3284144,3284673,3284144,3284673,3284144,3284673,3284144,3284673,3284144,3284673,3284144,3284673,3284144,3284673,3284144,3284673,3284144,3284673,3284144,3284673,3284144,3284673,3284673,3284673</t>
+          <t>3284136,3284019,3284242,3284019,3284668,3284253,3284136,3284019,3284242,3284019,3284668,3284253,3284136,3284019,3284242,3284019,3284668,3284253,3284136,3284091,3284242,3284091,3284668,3284645,3284136,3284091,3284242,3284091,3284668,3284645,3284136,3284099,3284242,3284099,3284668,3284693,3284136,3284099,3284786,3284099,3284868,3284693,3284136,3284099,3284786,3284099,3284868,3284693,3284136,3284107,3284786,3284107,3284868,3284709,3284136,3284107,3284786,3284107,3284868,3284709,3284136,3284107,3284786,3284107,3284868,3284136,3284115,3284786,3284115,3284988,3284136,3284115,3284115,3284988,3284144,3284673,3284988,3284144,3284673,3284988,3284144,3284673,3284988,3284144,3284673,3284144,3284673,3284144,3284673,3284144,3284673,3284144,3284673,3284144,3284673,3284144,3284673,3284144,3284673,3284144,3284673,3284144,3284673,3284144,3284673,3284673,3284673</t>
         </is>
       </c>
       <c r="D18" s="0" t="n">
@@ -1463,7 +1463,7 @@
       </c>
       <c r="F18" s="0" t="inlineStr">
         <is>
-          <t>L5 W13/25; N=107; EHP=3560.000000; air:2x3,air:11x2,air:12x3,air:13x3,air:14x2,normal:17x13,normal:18x14,fast:30x6,heavy:31x3,heavy:80x2,medium:83x6,swarm:84x29,heavy:86x3,heavy:88x2,fast:98x6,medium:108x5,medium:123x5</t>
+          <t>L5 W13/25; N=107; EHP=6582.233542; air:2x6,air:11x4,air:12x6,air:13x6,air:14x4,fast:30x6,fast:98x6,heavy:31x3,heavy:80x2,heavy:86x3,heavy:88x2,medium:83x6,medium:108x5,medium:123x5,normal:17x13,normal:18x14,swarm:84x16 | manual: L1-scaled</t>
         </is>
       </c>
     </row>
@@ -1473,7 +1473,7 @@
       </c>
       <c r="C19" s="0" t="inlineStr">
         <is>
-          <t>3286136,3286673,3286242,3286019,3286668,3286253,3286136,3286673,3286242,3286019,3286668,3286253,3286136,3286673,3286242,3286019,3286668,3286253,3286136,3286673,3286242,3286091,3286668,3286645,3286136,3286673,3286242,3286091,3286668,3286645,3286136,3286673,3286242,3286091,3286868,3286645,3286136,3286673,3286786,3286099,3286868,3286693,3286136,3286673,3286786,3286099,3286868,3286693,3286136,3286673,3286786,3286107,3286868,3286709,3286136,3286673,3286786,3286107,3286868,3286709,3286136,3286673,3286786,3286107,3286988,3286709,3286136,3286673,3286786,3286115,3286988,3286136,3286673,3286786,3286115,3286988,3286136,3286673,3286115,3286988,3286144,3286673,3286988,3286144,3286673,3286988,3286144,3286673,3286144,3286673,3286144,3286673,3286144,3286673,3286144,3286673,3286144,3286673,3286144,3286673,3286144,3286673,3286144,3286673,3286144,3286673,3286144,3286673,3286144,3286673,3286673,3286673,3286673</t>
+          <t>3286136,3286019,3286242,3286019,3286668,3286253,3286136,3286019,3286242,3286019,3286668,3286253,3286136,3286019,3286242,3286019,3286668,3286253,3286136,3286091,3286242,3286091,3286668,3286645,3286136,3286091,3286242,3286091,3286668,3286645,3286136,3286091,3286242,3286091,3286868,3286645,3286136,3286099,3286786,3286099,3286868,3286693,3286136,3286099,3286786,3286099,3286868,3286693,3286136,3286107,3286786,3286107,3286868,3286709,3286136,3286107,3286786,3286107,3286868,3286709,3286136,3286107,3286786,3286107,3286988,3286709,3286136,3286115,3286786,3286115,3286988,3286136,3286115,3286786,3286115,3286988,3286136,3286115,3286115,3286988,3286144,3286673,3286988,3286144,3286673,3286988,3286144,3286673,3286144,3286673,3286144,3286673,3286144,3286673,3286144,3286673,3286144,3286673,3286144,3286673,3286144,3286673,3286144,3286673,3286144,3286673,3286144,3286673,3286144,3286673,3286673,3286673,3286673</t>
         </is>
       </c>
       <c r="D19" s="0" t="n">
@@ -1484,7 +1484,7 @@
       </c>
       <c r="F19" s="0" t="inlineStr">
         <is>
-          <t>L5 W14/25; N=113; EHP=4298.000000; air:2x3,air:11x3,air:12x2,air:13x3,air:14x3,normal:17x14,normal:18x14,fast:30x6,heavy:31x3,heavy:80x3,medium:83x5,swarm:84x31,heavy:86x2,heavy:88x3,fast:98x7,medium:108x5,medium:123x6</t>
+          <t>L5 W14/25; N=113; EHP=7948.911865; air:2x6,air:11x6,air:12x4,air:13x6,air:14x6,fast:30x6,fast:98x7,heavy:31x3,heavy:80x3,heavy:86x2,heavy:88x3,medium:83x5,medium:108x5,medium:123x6,normal:17x14,normal:18x14,swarm:84x17 | manual: L1-scaled</t>
         </is>
       </c>
     </row>
@@ -1494,7 +1494,7 @@
       </c>
       <c r="C20" s="0" t="inlineStr">
         <is>
-          <t>3288136,3288673,3288242,3288019,3288668,3288253,3288254,3288136,3288673,3288242,3288019,3288668,3288253,3288136,3288673,3288242,3288091,3288668,3288645,3288136,3288673,3288242,3288091,3288668,3288645,3288136,3288673,3288242,3288091,3288668,3288645,3288136,3288673,3288242,3288099,3288668,3288693,3288136,3288673,3288242,3288099,3288868,3288693,3288136,3288673,3288786,3288099,3288868,3288693,3288136,3288673,3288786,3288107,3288868,3288709,3288136,3288673,3288786,3288107,3288868,3288709,3288136,3288673,3288786,3288107,3288868,3288709,3288136,3288673,3288786,3288115,3288868,3288136,3288673,3288786,3288115,3288988,3288136,3288673,3288786,3288115,3288988,3288144,3288673,3288988,3288144,3288673,3288988,3288144,3288673,3288988,3288144,3288673,3288144,3288673,3288144,3288673,3288144,3288673,3288144,3288673,3288144,3288673,3288144,3288673,3288144,3288673,3288144,3288673,3288144,3288673,3288144,3288673,3288144,3288673,3288673,3288673,3288673,3288673</t>
+          <t>3288136,3288019,3288242,3288019,3288668,3288253,3288254,3288136,3288019,3288242,3288019,3288668,3288253,3288136,3288091,3288242,3288091,3288668,3288645,3288136,3288091,3288242,3288091,3288668,3288645,3288136,3288091,3288242,3288091,3288668,3288645,3288136,3288099,3288242,3288099,3288668,3288693,3288136,3288099,3288242,3288099,3288868,3288693,3288136,3288099,3288786,3288099,3288868,3288693,3288136,3288107,3288786,3288107,3288868,3288709,3288136,3288107,3288786,3288107,3288868,3288709,3288136,3288107,3288786,3288107,3288868,3288709,3288136,3288115,3288786,3288115,3288868,3288136,3288115,3288786,3288115,3288988,3288136,3288115,3288786,3288115,3288988,3288144,3288673,3288988,3288144,3288673,3288988,3288144,3288673,3288988,3288144,3288673,3288144,3288673,3288144,3288673,3288144,3288673,3288144,3288673,3288144,3288673,3288144,3288673,3288144,3288673,3288144,3288673,3288144,3288673,3288144,3288673,3288144,3288673,3288673,3288673,3288673,3288673</t>
         </is>
       </c>
       <c r="D20" s="0" t="n">
@@ -1505,7 +1505,7 @@
       </c>
       <c r="F20" s="0" t="inlineStr">
         <is>
-          <t>L5 W15/25; N=119; EHP=7501.000000; air:2x2,air:11x3,air:12x3,air:13x3,air:14x3,normal:17x14,normal:18x15,fast:30x7,elite:31x1,heavy:31x2,heavy:80x3,medium:83x6,swarm:84x33,heavy:86x3,heavy:88x3,fast:98x7,medium:108x6,medium:123x5</t>
+          <t>L5 W15/25; N=119; EHP=13860.163175; air:2x4,air:11x6,air:12x6,air:13x6,air:14x6,elite:31x1,fast:30x7,fast:98x7,heavy:31x2,heavy:80x3,heavy:86x3,heavy:88x3,medium:83x6,medium:108x6,medium:123x5,normal:17x14,normal:18x15,swarm:84x19 | manual: L1-scaled</t>
         </is>
       </c>
     </row>
@@ -1515,7 +1515,7 @@
       </c>
       <c r="C21" s="0" t="inlineStr">
         <is>
-          <t>3290136,3290673,3290242,3290019,3290668,3290253,3290136,3290673,3290242,3290019,3290668,3290253,3290136,3290673,3290242,3290019,3290668,3290253,3290136,3290673,3290242,3290091,3290668,3290645,3290136,3290673,3290242,3290091,3290668,3290645,3290136,3290673,3290242,3290091,3290668,3290645,3290136,3290673,3290242,3290099,3290868,3290693,3290136,3290673,3290786,3290099,3290868,3290693,3290136,3290673,3290786,3290099,3290868,3290693,3290136,3290673,3290786,3290107,3290868,3290709,3290136,3290673,3290786,3290107,3290868,3290709,3290136,3290673,3290786,3290107,3290868,3290709,3290136,3290673,3290786,3290115,3290988,3290136,3290673,3290786,3290115,3290988,3290136,3290673,3290786,3290115,3290988,3290144,3290673,3290988,3290144,3290673,3290988,3290144,3290673,3290988,3290144,3290673,3290144,3290673,3290144,3290673,3290144,3290673,3290144,3290673,3290144,3290673,3290144,3290673,3290144,3290673,3290144,3290673,3290144,3290673,3290144,3290673,3290144,3290673,3290673,3290673,3290673,3290673,3290673</t>
+          <t>3290136,3290019,3290242,3290019,3290668,3290253,3290136,3290019,3290242,3290019,3290668,3290253,3290136,3290019,3290242,3290019,3290668,3290253,3290136,3290091,3290242,3290091,3290668,3290645,3290136,3290091,3290242,3290091,3290668,3290645,3290136,3290091,3290242,3290091,3290668,3290645,3290136,3290099,3290242,3290099,3290868,3290693,3290136,3290099,3290786,3290099,3290868,3290693,3290136,3290099,3290786,3290099,3290868,3290693,3290136,3290107,3290786,3290107,3290868,3290709,3290136,3290107,3290786,3290107,3290868,3290709,3290136,3290107,3290786,3290107,3290868,3290709,3290136,3290115,3290786,3290115,3290988,3290136,3290115,3290786,3290115,3290988,3290136,3290115,3290786,3290115,3290988,3290144,3290673,3290988,3290144,3290673,3290988,3290144,3290673,3290988,3290144,3290673,3290144,3290673,3290144,3290673,3290144,3290673,3290144,3290673,3290144,3290673,3290144,3290673,3290144,3290673,3290144,3290673,3290144,3290673,3290144,3290673,3290144,3290673,3290673,3290673,3290673,3290673,3290673</t>
         </is>
       </c>
       <c r="D21" s="0" t="n">
@@ -1526,7 +1526,7 @@
       </c>
       <c r="F21" s="0" t="inlineStr">
         <is>
-          <t>L5 W16/25; N=125; EHP=7652.000000; air:2x3,air:11x3,air:12x3,air:13x3,air:14x3,normal:17x15,normal:18x15,fast:30x7,heavy:31x3,heavy:80x3,medium:83x6,swarm:84x35,heavy:86x3,heavy:88x3,fast:98x8,medium:108x6,medium:123x6</t>
+          <t>L5 W16/25; N=125; EHP=14146.765160; air:2x6,air:11x6,air:12x6,air:13x6,air:14x6,fast:30x7,fast:98x8,heavy:31x3,heavy:80x3,heavy:86x3,heavy:88x3,medium:83x6,medium:108x6,medium:123x6,normal:17x15,normal:18x15,swarm:84x20 | manual: L1-scaled</t>
         </is>
       </c>
     </row>
@@ -1536,7 +1536,7 @@
       </c>
       <c r="C22" s="0" t="inlineStr">
         <is>
-          <t>3292136,3292673,3292242,3292019,3292668,3292253,3292136,3292673,3292242,3292019,3292668,3292253,3292136,3292673,3292242,3292019,3292668,3292253,3292136,3292673,3292242,3292091,3292668,3292645,3292136,3292673,3292242,3292091,3292668,3292645,3292136,3292673,3292242,3292091,3292668,3292645,3292136,3292673,3292242,3292099,3292868,3292693,3292136,3292673,3292242,3292099,3292868,3292693,3292136,3292673,3292786,3292099,3292868,3292693,3292136,3292673,3292786,3292107,3292868,3292693,3292136,3292673,3292786,3292107,3292868,3292709,3292136,3292673,3292786,3292107,3292868,3292709,3292136,3292673,3292786,3292115,3292988,3292709,3292136,3292673,3292786,3292115,3292988,3292136,3292673,3292786,3292115,3292988,3292136,3292673,3292115,3292988,3292144,3292673,3292988,3292144,3292673,3292988,3292144,3292673,3292988,3292144,3292673,3292144,3292673,3292144,3292673,3292144,3292673,3292144,3292673,3292144,3292673,3292144,3292673,3292144,3292673,3292144,3292673,3292144,3292673,3292144,3292673,3292144,3292673,3292144,3292673,3292673,3292673,3292673,3292673</t>
+          <t>3292136,3292019,3292242,3292019,3292668,3292253,3292136,3292019,3292242,3292019,3292668,3292253,3292136,3292019,3292242,3292019,3292668,3292253,3292136,3292091,3292242,3292091,3292668,3292645,3292136,3292091,3292242,3292091,3292668,3292645,3292136,3292091,3292242,3292091,3292668,3292645,3292136,3292099,3292242,3292099,3292868,3292693,3292136,3292099,3292242,3292099,3292868,3292693,3292136,3292099,3292786,3292099,3292868,3292693,3292136,3292107,3292786,3292107,3292868,3292693,3292136,3292107,3292786,3292107,3292868,3292709,3292136,3292107,3292786,3292107,3292868,3292709,3292136,3292115,3292786,3292115,3292988,3292709,3292136,3292115,3292786,3292115,3292988,3292136,3292115,3292786,3292115,3292988,3292136,3292115,3292115,3292988,3292144,3292673,3292988,3292144,3292673,3292988,3292144,3292673,3292988,3292144,3292673,3292144,3292673,3292144,3292673,3292144,3292673,3292144,3292673,3292144,3292673,3292144,3292673,3292144,3292673,3292144,3292673,3292144,3292673,3292144,3292673,3292144,3292673,3292144,3292673,3292673,3292673,3292673,3292673</t>
         </is>
       </c>
       <c r="D22" s="0" t="n">
@@ -1547,7 +1547,7 @@
       </c>
       <c r="F22" s="0" t="inlineStr">
         <is>
-          <t>L5 W17/25; N=131; EHP=7806.000000; air:2x3,air:11x3,air:12x3,air:13x3,air:14x4,normal:17x16,normal:18x16,fast:30x8,heavy:31x3,heavy:80x3,medium:83x6,swarm:84x36,heavy:86x4,heavy:88x3,fast:98x7,medium:108x6,medium:123x7</t>
+          <t>L5 W17/25; N=131; EHP=14433.439744; air:2x6,air:11x6,air:12x6,air:13x6,air:14x8,fast:30x8,fast:98x7,heavy:31x3,heavy:80x3,heavy:86x4,heavy:88x3,medium:83x6,medium:108x6,medium:123x7,normal:17x16,normal:18x16,swarm:84x20 | manual: L1-scaled</t>
         </is>
       </c>
     </row>
@@ -1557,7 +1557,7 @@
       </c>
       <c r="C23" s="0" t="inlineStr">
         <is>
-          <t>3294136,3294673,3294242,3294019,3294668,3294253,3294136,3294673,3294242,3294019,3294668,3294253,3294136,3294673,3294242,3294019,3294668,3294253,3294136,3294673,3294242,3294091,3294668,3294253,3294136,3294673,3294242,3294091,3294668,3294645,3294136,3294673,3294242,3294091,3294668,3294645,3294136,3294673,3294242,3294099,3294668,3294645,3294136,3294673,3294242,3294099,3294868,3294693,3294136,3294673,3294786,3294099,3294868,3294693,3294136,3294673,3294786,3294099,3294868,3294693,3294136,3294673,3294786,3294107,3294868,3294709,3294136,3294673,3294786,3294107,3294868,3294709,3294136,3294673,3294786,3294107,3294868,3294709,3294136,3294673,3294786,3294115,3294868,3294136,3294673,3294786,3294115,3294988,3294136,3294673,3294786,3294115,3294988,3294136,3294673,3294988,3294144,3294673,3294988,3294144,3294673,3294988,3294144,3294673,3294988,3294144,3294673,3294144,3294673,3294144,3294673,3294144,3294673,3294144,3294673,3294144,3294673,3294144,3294673,3294144,3294673,3294144,3294673,3294144,3294673,3294144,3294673,3294144,3294673,3294144,3294673,3294144,3294673,3294673,3294673,3294673,3294673</t>
+          <t>3294136,3294019,3294242,3294019,3294668,3294253,3294136,3294019,3294242,3294019,3294668,3294253,3294136,3294019,3294242,3294019,3294668,3294253,3294136,3294091,3294242,3294091,3294668,3294253,3294136,3294091,3294242,3294091,3294668,3294645,3294136,3294091,3294242,3294091,3294668,3294645,3294136,3294099,3294242,3294099,3294668,3294645,3294136,3294099,3294242,3294099,3294868,3294693,3294136,3294099,3294786,3294099,3294868,3294693,3294136,3294099,3294786,3294099,3294868,3294693,3294136,3294107,3294786,3294107,3294868,3294709,3294136,3294107,3294786,3294107,3294868,3294709,3294136,3294107,3294786,3294107,3294868,3294709,3294136,3294115,3294786,3294115,3294868,3294136,3294115,3294786,3294115,3294988,3294136,3294115,3294786,3294115,3294988,3294136,3294673,3294988,3294144,3294673,3294988,3294144,3294673,3294988,3294144,3294673,3294988,3294144,3294673,3294144,3294673,3294144,3294673,3294144,3294673,3294144,3294673,3294144,3294673,3294144,3294673,3294144,3294673,3294144,3294673,3294144,3294673,3294144,3294673,3294144,3294673,3294144,3294673,3294144,3294673,3294673,3294673,3294673,3294673</t>
         </is>
       </c>
       <c r="D23" s="0" t="n">
@@ -1568,7 +1568,7 @@
       </c>
       <c r="F23" s="0" t="inlineStr">
         <is>
-          <t>L5 W18/25; N=137; EHP=8342.000000; air:2x3,air:11x3,air:12x4,air:13x3,air:14x3,normal:17x17,normal:18x17,fast:30x8,heavy:31x4,heavy:80x3,medium:83x7,swarm:84x38,heavy:86x3,heavy:88x3,fast:98x8,medium:108x7,medium:123x6</t>
+          <t>L5 W18/25; N=137; EHP=15417.143429; air:2x6,air:11x6,air:12x8,air:13x6,air:14x6,fast:30x8,fast:98x8,heavy:31x4,heavy:80x3,heavy:86x3,heavy:88x3,medium:83x7,medium:108x7,medium:123x6,normal:17x17,normal:18x17,swarm:84x22 | manual: L1-scaled</t>
         </is>
       </c>
     </row>
@@ -1578,7 +1578,7 @@
       </c>
       <c r="C24" s="0" t="inlineStr">
         <is>
-          <t>3296136,3296673,3296242,3296019,3296668,3296253,3296136,3296673,3296242,3296019,3296668,3296253,3296136,3296673,3296242,3296019,3296668,3296253,3296136,3296673,3296242,3296019,3296668,3296645,3296136,3296673,3296242,3296091,3296668,3296645,3296136,3296673,3296242,3296091,3296668,3296645,3296136,3296673,3296242,3296091,3296668,3296645,3296136,3296673,3296242,3296099,3296868,3296693,3296136,3296673,3296242,3296099,3296868,3296693,3296136,3296673,3296786,3296099,3296868,3296693,3296136,3296673,3296786,3296107,3296868,3296709,3296136,3296673,3296786,3296107,3296868,3296709,3296136,3296673,3296786,3296107,3296868,3296709,3296136,3296673,3296786,3296107,3296868,3296709,3296136,3296673,3296786,3296115,3296988,3296136,3296673,3296786,3296115,3296988,3296136,3296673,3296786,3296115,3296988,3296144,3296673,3296988,3296144,3296673,3296988,3296144,3296673,3296988,3296144,3296673,3296988,3296144,3296673,3296144,3296673,3296144,3296673,3296144,3296673,3296144,3296673,3296144,3296673,3296144,3296673,3296144,3296673,3296144,3296673,3296144,3296673,3296144,3296673,3296144,3296673,3296144,3296673,3296673,3296673,3296673,3296673,3296673,3296673</t>
+          <t>3296136,3296019,3296242,3296019,3296668,3296253,3296136,3296019,3296242,3296019,3296668,3296253,3296136,3296019,3296242,3296019,3296668,3296253,3296136,3296019,3296242,3296019,3296668,3296645,3296136,3296091,3296242,3296091,3296668,3296645,3296136,3296091,3296242,3296091,3296668,3296645,3296136,3296091,3296242,3296091,3296668,3296645,3296136,3296099,3296242,3296099,3296868,3296693,3296136,3296099,3296242,3296099,3296868,3296693,3296136,3296099,3296786,3296099,3296868,3296693,3296136,3296107,3296786,3296107,3296868,3296709,3296136,3296107,3296786,3296107,3296868,3296709,3296136,3296107,3296786,3296107,3296868,3296709,3296136,3296107,3296786,3296107,3296868,3296709,3296136,3296115,3296786,3296115,3296988,3296136,3296115,3296786,3296115,3296988,3296136,3296115,3296786,3296115,3296988,3296144,3296673,3296988,3296144,3296673,3296988,3296144,3296673,3296988,3296144,3296673,3296988,3296144,3296673,3296144,3296673,3296144,3296673,3296144,3296673,3296144,3296673,3296144,3296673,3296144,3296673,3296144,3296673,3296144,3296673,3296144,3296673,3296144,3296673,3296144,3296673,3296144,3296673,3296673,3296673,3296673,3296673,3296673,3296673</t>
         </is>
       </c>
       <c r="D24" s="0" t="n">
@@ -1589,7 +1589,7 @@
       </c>
       <c r="F24" s="0" t="inlineStr">
         <is>
-          <t>L5 W19/25; N=143; EHP=9660.000000; air:2x4,air:11x3,air:12x3,air:13x4,air:14x3,normal:17x17,normal:18x17,fast:30x9,heavy:31x3,heavy:80x4,medium:83x7,swarm:84x40,heavy:86x3,heavy:88x4,fast:98x8,medium:108x7,medium:123x7</t>
+          <t>L5 W19/25; N=143; EHP=17856.170931; air:2x8,air:11x6,air:12x6,air:13x8,air:14x6,fast:30x9,fast:98x8,heavy:31x3,heavy:80x4,heavy:86x3,heavy:88x4,medium:83x7,medium:108x7,medium:123x7,normal:17x17,normal:18x17,swarm:84x23 | manual: L1-scaled</t>
         </is>
       </c>
     </row>
@@ -1599,7 +1599,7 @@
       </c>
       <c r="C25" s="0" t="inlineStr">
         <is>
-          <t>3298136,3298673,3298242,3298019,3298668,3298253,3298254,3298136,3298673,3298242,3298019,3298668,3298253,3298136,3298673,3298242,3298019,3298668,3298253,3298136,3298673,3298242,3298091,3298668,3298645,3298136,3298673,3298242,3298091,3298668,3298645,3298136,3298673,3298242,3298091,3298668,3298645,3298136,3298673,3298242,3298091,3298668,3298645,3298136,3298673,3298242,3298099,3298868,3298693,3298136,3298673,3298786,3298099,3298868,3298693,3298136,3298673,3298786,3298099,3298868,3298693,3298136,3298673,3298786,3298107,3298868,3298693,3298136,3298673,3298786,3298107,3298868,3298709,3298136,3298673,3298786,3298107,3298868,3298709,3298136,3298673,3298786,3298107,3298868,3298709,3298136,3298673,3298786,3298115,3298988,3298136,3298673,3298786,3298115,3298988,3298136,3298673,3298786,3298115,3298988,3298136,3298673,3298115,3298988,3298144,3298673,3298988,3298144,3298673,3298988,3298144,3298673,3298988,3298144,3298673,3298988,3298144,3298673,3298144,3298673,3298144,3298673,3298144,3298673,3298144,3298673,3298144,3298673,3298144,3298673,3298144,3298673,3298144,3298673,3298144,3298673,3298144,3298673,3298144,3298673,3298144,3298673,3298144,3298673,3298673,3298673,3298673,3298673,3298673</t>
+          <t>3298136,3298019,3298242,3298019,3298668,3298253,3298254,3298136,3298019,3298242,3298019,3298668,3298253,3298136,3298019,3298242,3298019,3298668,3298253,3298136,3298091,3298242,3298091,3298668,3298645,3298136,3298091,3298242,3298091,3298668,3298645,3298136,3298091,3298242,3298091,3298668,3298645,3298136,3298091,3298242,3298091,3298668,3298645,3298136,3298099,3298242,3298099,3298868,3298693,3298136,3298099,3298786,3298099,3298868,3298693,3298136,3298099,3298786,3298099,3298868,3298693,3298136,3298107,3298786,3298107,3298868,3298693,3298136,3298107,3298786,3298107,3298868,3298709,3298136,3298107,3298786,3298107,3298868,3298709,3298136,3298107,3298786,3298107,3298868,3298709,3298136,3298115,3298786,3298115,3298988,3298136,3298115,3298786,3298115,3298988,3298136,3298115,3298786,3298115,3298988,3298136,3298115,3298115,3298988,3298144,3298673,3298988,3298144,3298673,3298988,3298144,3298673,3298988,3298144,3298673,3298988,3298144,3298673,3298144,3298673,3298144,3298673,3298144,3298673,3298144,3298673,3298144,3298673,3298144,3298673,3298144,3298673,3298144,3298673,3298144,3298673,3298144,3298673,3298144,3298673,3298144,3298673,3298144,3298673,3298673,3298673,3298673,3298673,3298673</t>
         </is>
       </c>
       <c r="D25" s="0" t="n">
@@ -1610,7 +1610,7 @@
       </c>
       <c r="F25" s="0" t="inlineStr">
         <is>
-          <t>L5 W20/25; N=149; EHP=16226.000000; air:2x3,air:11x4,air:12x3,air:13x4,air:14x4,normal:17x18,normal:18x18,fast:30x8,elite:31x1,heavy:31x3,heavy:80x4,medium:83x7,swarm:84x41,heavy:86x4,heavy:88x3,fast:98x9,medium:108x7,medium:123x8</t>
+          <t>L5 W20/25; N=149; EHP=29991.349799; air:2x6,air:11x8,air:12x6,air:13x8,air:14x8,elite:31x1,fast:30x8,fast:98x9,heavy:31x3,heavy:80x4,heavy:86x4,heavy:88x3,medium:83x7,medium:108x7,medium:123x8,normal:17x18,normal:18x18,swarm:84x23 | manual: L1-scaled</t>
         </is>
       </c>
     </row>
@@ -1620,7 +1620,7 @@
       </c>
       <c r="C26" s="0" t="inlineStr">
         <is>
-          <t>10017006,10017012,10017008,10048514,10017011,10017009,10017006,10017012,10017008,10048514,10017011,10017009,10017006,10017012,10017008,10048514,10017011,10017009,10017006,10017012,10017008,10048514,10017011,10017009,10017006,10017012,10017008,10017003,10017011,10017010,10017006,10017012,10017008,10017003,10017011,10017010,10017006,10017012,10017008,10017003,10017011,10017010,10017006,10017012,10017008,10017003,10017011,10017010,10017006,10017012,10017008,10048515,10017016,10017013,10017006,10017012,10017008,10048515,10017016,10017013,10017006,10017012,10017015,10048515,10017016,10017013,10017006,10017012,10017015,10048515,10017016,10017013,10017006,10017012,10017015,10017004,10017016,10017014,10017006,10017012,10017015,10017004,10017016,10017014,10017006,10017012,10017015,10017004,10017016,10017014,10017006,10017012,10017015,10017004,10017016,10017014,10017006,10017012,10017015,10017005,10017017,10017006,10017012,10017015,10017005,10017017,10017006,10017012,10017015,10017005,10017017,10017006,10017012,10017015,10017005,10017017,10017007,10017012,10017017,10017007,10017012,10017017,10017007,10017012,10017017,10017007,10017012,10017017,10017007,10017012,10017017,10017007,10017012,10017007,10017012,10017007,10017012,10017007,10017012,10017007,10017012,10017007,10017012,10017007,10017012,10017007,10017012,10017007,10017012,10017007,10017012,10017007,10017012,10017007,10017012,10017007,10017012,10017007,10017012,10017007,10017012,10017012,10017012,10017012,10017012,10017012,10017012</t>
+          <t>10017006,10048514,10017008,10048514,10017011,10017009,10017006,10048514,10017008,10048514,10017011,10017009,10017006,10048514,10017008,10048514,10017011,10017009,10017006,10048514,10017008,10048514,10017011,10017009,10017006,10017003,10017008,10017003,10017011,10017010,10017006,10017003,10017008,10017003,10017011,10017010,10017006,10017003,10017008,10017003,10017011,10017010,10017006,10017003,10017008,10017003,10017011,10017010,10017006,10048515,10017008,10048515,10017016,10017013,10017006,10048515,10017008,10048515,10017016,10017013,10017006,10048515,10017015,10048515,10017016,10017013,10017006,10048515,10017015,10048515,10017016,10017013,10017006,10017004,10017015,10017004,10017016,10017014,10017006,10017004,10017015,10017004,10017016,10017014,10017006,10017004,10017015,10017004,10017016,10017014,10017006,10017004,10017015,10017004,10017016,10017014,10017006,10017005,10017015,10017005,10017017,10017006,10017005,10017015,10017005,10017017,10017006,10017005,10017015,10017005,10017017,10017006,10017005,10017015,10017005,10017017,10017007,10017012,10017017,10017007,10017012,10017017,10017007,10017012,10017017,10017007,10017012,10017017,10017007,10017012,10017017,10017007,10017012,10017007,10017012,10017007,10017012,10017007,10017012,10017007,10017012,10017007,10017012,10017007,10017012,10017007,10017012,10017007,10017012,10017007,10017012,10017007,10017012,10017007,10017012,10017007,10017012,10017007,10017012,10017007,10017012,10017012,10017012,10017012,10017012,10017012,10017012</t>
         </is>
       </c>
       <c r="D26" s="3" t="n">
@@ -1631,7 +1631,7 @@
       </c>
       <c r="F26" s="0" t="inlineStr">
         <is>
-          <t>L5 W23/25; N=167; EHP=17221.000000; air:2x4,air:11x4,air:12x4,air:13x4,air:14x4,normal:17x20,normal:18x20,fast:30x10,heavy:31x4,heavy:80x4,medium:83x8,swarm:84x46,heavy:86x4,heavy:88x4,fast:98x10,medium:108x8,medium:123x9</t>
+          <t>L5 W23/25; N=167; EHP=31834.951643; air:2x8,air:11x8,air:12x8,air:13x8,air:14x8,fast:30x10,fast:98x10,heavy:31x4,heavy:80x4,heavy:86x4,heavy:88x4,medium:83x8,medium:108x8,medium:123x9,normal:17x20,normal:18x20,swarm:84x26 | manual: L1-scaled</t>
         </is>
       </c>
     </row>
@@ -1641,7 +1641,7 @@
       </c>
       <c r="C27" s="0" t="inlineStr">
         <is>
-          <t>10017021,10017027,10017023,10048516,10017026,10017024,10017021,10017027,10017023,10048516,10017026,10017024,10017021,10017027,10017023,10048516,10017026,10017024,10017021,10017027,10017023,10048516,10017026,10017024,10017021,10017027,10017023,10048516,10017026,10017025,10017021,10017027,10017023,10017018,10017026,10017025,10017021,10017027,10017023,10017018,10017026,10017025,10017021,10017027,10017023,10017018,10017026,10017025,10017021,10017027,10017023,10017018,10017031,10017025,10017021,10017027,10017023,10048517,10017031,10017028,10017021,10017027,10017030,10048517,10017031,10017028,10017021,10017027,10017030,10048517,10017031,10017028,10017021,10017027,10017030,10048517,10017031,10017028,10017021,10017027,10017030,10017019,10017031,10017029,10017021,10017027,10017030,10017019,10017031,10017029,10017021,10017027,10017030,10017019,10017031,10017029,10017021,10017027,10017030,10017019,10017031,10017029,10017021,10017027,10017030,10017020,10017032,10017021,10017027,10017030,10017020,10017032,10017021,10017027,10017030,10017020,10017032,10017021,10017027,10017020,10017032,10017022,10017027,10017032,10017022,10017027,10017032,10017022,10017027,10017032,10017022,10017027,10017032,10017022,10017027,10017022,10017027,10017022,10017027,10017022,10017027,10017022,10017027,10017022,10017027,10017022,10017027,10017022,10017027,10017022,10017027,10017022,10017027,10017022,10017027,10017022,10017027,10017022,10017027,10017022,10017027,10017022,10017027,10017022,10017027,10017022,10017027,10017027,10017027,10017027,10017027,10017027,10017027</t>
+          <t>10017021,10048516,10017023,10048516,10017026,10017024,10017021,10048516,10017023,10048516,10017026,10017024,10017021,10048516,10017023,10048516,10017026,10017024,10017021,10048516,10017023,10048516,10017026,10017024,10017021,10048516,10017023,10048516,10017026,10017025,10017021,10017018,10017023,10017018,10017026,10017025,10017021,10017018,10017023,10017018,10017026,10017025,10017021,10017018,10017023,10017018,10017026,10017025,10017021,10017018,10017023,10017018,10017031,10017025,10017021,10048517,10017023,10048517,10017031,10017028,10017021,10048517,10017030,10048517,10017031,10017028,10017021,10048517,10017030,10048517,10017031,10017028,10017021,10048517,10017030,10048517,10017031,10017028,10017021,10017019,10017030,10017019,10017031,10017029,10017021,10017019,10017030,10017019,10017031,10017029,10017021,10017019,10017030,10017019,10017031,10017029,10017021,10017019,10017030,10017019,10017031,10017029,10017021,10017020,10017030,10017020,10017032,10017021,10017020,10017030,10017020,10017032,10017021,10017020,10017030,10017020,10017032,10017021,10017020,10017020,10017032,10017022,10017027,10017032,10017022,10017027,10017032,10017022,10017027,10017032,10017022,10017027,10017032,10017022,10017027,10017022,10017027,10017022,10017027,10017022,10017027,10017022,10017027,10017022,10017027,10017022,10017027,10017022,10017027,10017022,10017027,10017022,10017027,10017022,10017027,10017022,10017027,10017022,10017027,10017022,10017027,10017022,10017027,10017022,10017027,10017022,10017027,10017027,10017027,10017027,10017027,10017027,10017027</t>
         </is>
       </c>
       <c r="D27" s="3" t="n">
@@ -1652,7 +1652,7 @@
       </c>
       <c r="F27" s="0" t="inlineStr">
         <is>
-          <t>L5 W24/25; N=173; EHP=18440.000000; air:2x5,air:11x4,air:12x4,air:13x4,air:14x4,normal:17x21,normal:18x21,fast:30x10,heavy:31x4,heavy:80x5,medium:83x8,swarm:84x48,heavy:86x4,heavy:88x4,fast:98x10,medium:108x9,medium:123x8</t>
+          <t>L5 W24/25; N=173; EHP=34094.313209; air:2x10,air:11x8,air:12x8,air:13x8,air:14x8,fast:30x10,fast:98x10,heavy:31x4,heavy:80x5,heavy:86x4,heavy:88x4,medium:83x8,medium:108x9,medium:123x8,normal:17x21,normal:18x21,swarm:84x27 | manual: L1-scaled</t>
         </is>
       </c>
     </row>
@@ -1662,7 +1662,7 @@
       </c>
       <c r="C28" s="0" t="inlineStr">
         <is>
-          <t>10017036,10017042,10017038,10048518,10017041,10017039,10017047,10017036,10017042,10017038,10048518,10017041,10017039,10017036,10017042,10017038,10048518,10017041,10017039,10017036,10017042,10017038,10048518,10017041,10017039,10017036,10017042,10017038,10017033,10017041,10017040,10017036,10017042,10017038,10017033,10017041,10017040,10017036,10017042,10017038,10017033,10017041,10017040,10017036,10017042,10017038,10017033,10017041,10017040,10017036,10017042,10017038,10048519,10017041,10017043,10017036,10017042,10017038,10048519,10017046,10017043,10017036,10017042,10017038,10048519,10017046,10017043,10017036,10017042,10017045,10048519,10017046,10017043,10017036,10017042,10017045,10017034,10017046,10017043,10017036,10017042,10017045,10017034,10017046,10017044,10017036,10017042,10017045,10017034,10017046,10017044,10017036,10017042,10017045,10017034,10017046,10017044,10017036,10017042,10017045,10017034,10017046,10017044,10017036,10017042,10017045,10017035,10017048,10017036,10017042,10017045,10017035,10017048,10017036,10017042,10017045,10017035,10017048,10017036,10017042,10017045,10017035,10017048,10017037,10017042,10017048,10017037,10017042,10017048,10017037,10017042,10017048,10017037,10017042,10017048,10017037,10017042,10017048,10017037,10017042,10017037,10017042,10017037,10017042,10017037,10017042,10017037,10017042,10017037,10017042,10017037,10017042,10017037,10017042,10017037,10017042,10017037,10017042,10017037,10017042,10017037,10017042,10017037,10017042,10017037,10017042,10017037,10017042,10017037,10017042,10017037,10017042,10017042,10017042,10017042,10017042,10017042,10017042,10017042</t>
+          <t>10017036,10048518,10017038,10048518,10017041,10017039,10017047,10017036,10048518,10017038,10048518,10017041,10017039,10017036,10048518,10017038,10048518,10017041,10017039,10017036,10048518,10017038,10048518,10017041,10017039,10017036,10017033,10017038,10017033,10017041,10017040,10017036,10017033,10017038,10017033,10017041,10017040,10017036,10017033,10017038,10017033,10017041,10017040,10017036,10017033,10017038,10017033,10017041,10017040,10017036,10048519,10017038,10048519,10017041,10017043,10017036,10048519,10017038,10048519,10017046,10017043,10017036,10048519,10017038,10048519,10017046,10017043,10017036,10048519,10017045,10048519,10017046,10017043,10017036,10017034,10017045,10017034,10017046,10017043,10017036,10017034,10017045,10017034,10017046,10017044,10017036,10017034,10017045,10017034,10017046,10017044,10017036,10017034,10017045,10017034,10017046,10017044,10017036,10017034,10017045,10017034,10017046,10017044,10017036,10017035,10017045,10017035,10017048,10017036,10017035,10017045,10017035,10017048,10017036,10017035,10017045,10017035,10017048,10017036,10017035,10017045,10017035,10017048,10017037,10017042,10017048,10017037,10017042,10017048,10017037,10017042,10017048,10017037,10017042,10017048,10017037,10017042,10017048,10017037,10017042,10017037,10017042,10017037,10017042,10017037,10017042,10017037,10017042,10017037,10017042,10017037,10017042,10017037,10017042,10017037,10017042,10017037,10017042,10017037,10017042,10017037,10017042,10017037,10017042,10017037,10017042,10017037,10017042,10017037,10017042,10017037,10017042,10017042,10017042,10017042,10017042,10017042,10017042,10017042</t>
         </is>
       </c>
       <c r="D28" s="3" t="n">
@@ -1673,7 +1673,7 @@
       </c>
       <c r="F28" s="0" t="inlineStr">
         <is>
-          <t>L5 W25/25; N=179; EHP=36812.000000; air:2x4,air:11x4,air:12x4,air:13x5,air:14x4,normal:17x21,normal:18x22,fast:30x11,heavy:31x4,heavy:80x4,medium:83x9,swarm:84x50,heavy:86x5,heavy:88x4,fast:98x10,medium:108x8,elite:123x1,medium:123x9</t>
+          <t>L5 W25/25; N=179; EHP=68022.766118; air:2x8,air:11x8,air:12x8,air:13x10,air:14x8,elite:123x1,fast:30x11,fast:98x10,heavy:31x4,heavy:80x4,heavy:86x5,heavy:88x4,medium:83x9,medium:108x8,medium:123x9,normal:17x21,normal:18x22,swarm:84x29 | manual: L1-scaled</t>
         </is>
       </c>
     </row>

--- a/Luban/Config/Datas/Levels/L05/EnemyList.xlsx
+++ b/Luban/Config/Datas/Levels/L05/EnemyList.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" windowWidth="28125" windowHeight="12540" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Sheet2" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Sheet3" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet2" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet3" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="144525" fullCalcOnLoad="1"/>
@@ -1165,7 +1165,7 @@
         <v>0</v>
       </c>
       <c r="E4" s="0" t="n">
-        <v>132</v>
+        <v>320</v>
       </c>
       <c r="F4" s="0" t="inlineStr">
         <is>
@@ -1186,7 +1186,7 @@
         <v>0</v>
       </c>
       <c r="E5" s="0" t="n">
-        <v>128</v>
+        <v>175</v>
       </c>
       <c r="F5" s="0" t="inlineStr">
         <is>
@@ -1207,7 +1207,7 @@
         <v>0</v>
       </c>
       <c r="E6" s="0" t="n">
-        <v>272</v>
+        <v>350</v>
       </c>
       <c r="F6" s="0" t="inlineStr">
         <is>
@@ -1228,7 +1228,7 @@
         <v>0</v>
       </c>
       <c r="E7" s="0" t="n">
-        <v>265</v>
+        <v>310</v>
       </c>
       <c r="F7" s="0" t="inlineStr">
         <is>
@@ -1249,7 +1249,7 @@
         <v>0</v>
       </c>
       <c r="E8" s="0" t="n">
-        <v>258</v>
+        <v>270</v>
       </c>
       <c r="F8" s="0" t="inlineStr">
         <is>
@@ -1270,7 +1270,7 @@
         <v>0</v>
       </c>
       <c r="E9" s="0" t="n">
-        <v>251</v>
+        <v>340</v>
       </c>
       <c r="F9" s="0" t="inlineStr">
         <is>
@@ -1291,7 +1291,7 @@
         <v>0</v>
       </c>
       <c r="E10" s="0" t="n">
-        <v>244</v>
+        <v>340</v>
       </c>
       <c r="F10" s="0" t="inlineStr">
         <is>
@@ -1312,7 +1312,7 @@
         <v>0</v>
       </c>
       <c r="E11" s="0" t="n">
-        <v>237</v>
+        <v>290</v>
       </c>
       <c r="F11" s="0" t="inlineStr">
         <is>
@@ -1333,7 +1333,7 @@
         <v>0</v>
       </c>
       <c r="E12" s="0" t="n">
-        <v>230</v>
+        <v>240</v>
       </c>
       <c r="F12" s="0" t="inlineStr">
         <is>
@@ -1354,7 +1354,7 @@
         <v>0</v>
       </c>
       <c r="E13" s="0" t="n">
-        <v>223</v>
+        <v>300</v>
       </c>
       <c r="F13" s="0" t="inlineStr">
         <is>
@@ -1375,7 +1375,7 @@
         <v>0</v>
       </c>
       <c r="E14" s="0" t="n">
-        <v>216</v>
+        <v>185</v>
       </c>
       <c r="F14" s="0" t="inlineStr">
         <is>
@@ -1396,7 +1396,7 @@
         <v>0</v>
       </c>
       <c r="E15" s="0" t="n">
-        <v>209</v>
+        <v>280</v>
       </c>
       <c r="F15" s="0" t="inlineStr">
         <is>
@@ -1417,7 +1417,7 @@
         <v>0</v>
       </c>
       <c r="E16" s="0" t="n">
-        <v>202</v>
+        <v>250</v>
       </c>
       <c r="F16" s="0" t="inlineStr">
         <is>
@@ -1438,7 +1438,7 @@
         <v>0</v>
       </c>
       <c r="E17" s="0" t="n">
-        <v>195</v>
+        <v>330</v>
       </c>
       <c r="F17" s="0" t="inlineStr">
         <is>
@@ -1459,7 +1459,7 @@
         <v>0</v>
       </c>
       <c r="E18" s="0" t="n">
-        <v>188</v>
+        <v>260</v>
       </c>
       <c r="F18" s="0" t="inlineStr">
         <is>
@@ -1480,7 +1480,7 @@
         <v>0</v>
       </c>
       <c r="E19" s="0" t="n">
-        <v>181</v>
+        <v>280</v>
       </c>
       <c r="F19" s="0" t="inlineStr">
         <is>
@@ -1501,7 +1501,7 @@
         <v>0</v>
       </c>
       <c r="E20" s="0" t="n">
-        <v>174</v>
+        <v>180</v>
       </c>
       <c r="F20" s="0" t="inlineStr">
         <is>
@@ -1522,7 +1522,7 @@
         <v>0</v>
       </c>
       <c r="E21" s="0" t="n">
-        <v>167</v>
+        <v>310</v>
       </c>
       <c r="F21" s="0" t="inlineStr">
         <is>
@@ -1543,7 +1543,7 @@
         <v>0</v>
       </c>
       <c r="E22" s="0" t="n">
-        <v>160</v>
+        <v>230</v>
       </c>
       <c r="F22" s="0" t="inlineStr">
         <is>
@@ -1564,7 +1564,7 @@
         <v>0</v>
       </c>
       <c r="E23" s="0" t="n">
-        <v>153</v>
+        <v>280</v>
       </c>
       <c r="F23" s="0" t="inlineStr">
         <is>
@@ -1585,7 +1585,7 @@
         <v>0</v>
       </c>
       <c r="E24" s="0" t="n">
-        <v>146</v>
+        <v>220</v>
       </c>
       <c r="F24" s="0" t="inlineStr">
         <is>
@@ -1606,7 +1606,7 @@
         <v>0</v>
       </c>
       <c r="E25" s="0" t="n">
-        <v>139</v>
+        <v>250</v>
       </c>
       <c r="F25" s="0" t="inlineStr">
         <is>
@@ -1627,7 +1627,7 @@
         <v>0</v>
       </c>
       <c r="E26" s="0" t="n">
-        <v>128</v>
+        <v>280</v>
       </c>
       <c r="F26" s="0" t="inlineStr">
         <is>
@@ -1648,7 +1648,7 @@
         <v>0</v>
       </c>
       <c r="E27" s="0" t="n">
-        <v>128</v>
+        <v>350</v>
       </c>
       <c r="F27" s="0" t="inlineStr">
         <is>
@@ -1669,7 +1669,7 @@
         <v>0</v>
       </c>
       <c r="E28" s="0" t="n">
-        <v>128</v>
+        <v>185</v>
       </c>
       <c r="F28" s="0" t="inlineStr">
         <is>
